--- a/artfynd/A 3248-2025 artfynd.xlsx
+++ b/artfynd/A 3248-2025 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136951559</v>
       </c>
       <c r="B2" t="n">
-        <v>99270</v>
+        <v>99276</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -789,7 +789,7 @@
         <v>136957210</v>
       </c>
       <c r="B3" t="n">
-        <v>99270</v>
+        <v>99276</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -895,7 +895,7 @@
         <v>136957208</v>
       </c>
       <c r="B4" t="n">
-        <v>99355</v>
+        <v>99361</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1001,7 +1001,7 @@
         <v>136957209</v>
       </c>
       <c r="B5" t="n">
-        <v>99377</v>
+        <v>99383</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1107,7 +1107,7 @@
         <v>136957211</v>
       </c>
       <c r="B6" t="n">
-        <v>110070</v>
+        <v>110076</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1213,7 +1213,7 @@
         <v>136957212</v>
       </c>
       <c r="B7" t="n">
-        <v>110070</v>
+        <v>110076</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>

--- a/artfynd/A 3248-2025 artfynd.xlsx
+++ b/artfynd/A 3248-2025 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136951559</v>
       </c>
       <c r="B2" t="n">
-        <v>99276</v>
+        <v>99278</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -789,7 +789,7 @@
         <v>136957210</v>
       </c>
       <c r="B3" t="n">
-        <v>99276</v>
+        <v>99278</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -895,7 +895,7 @@
         <v>136957208</v>
       </c>
       <c r="B4" t="n">
-        <v>99361</v>
+        <v>99363</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1001,7 +1001,7 @@
         <v>136957209</v>
       </c>
       <c r="B5" t="n">
-        <v>99383</v>
+        <v>99385</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1107,7 +1107,7 @@
         <v>136957211</v>
       </c>
       <c r="B6" t="n">
-        <v>110076</v>
+        <v>110078</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1213,7 +1213,7 @@
         <v>136957212</v>
       </c>
       <c r="B7" t="n">
-        <v>110076</v>
+        <v>110078</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>

--- a/artfynd/A 3248-2025 artfynd.xlsx
+++ b/artfynd/A 3248-2025 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136951559</v>
       </c>
       <c r="B2" t="n">
-        <v>99278</v>
+        <v>99279</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -789,7 +789,7 @@
         <v>136957210</v>
       </c>
       <c r="B3" t="n">
-        <v>99278</v>
+        <v>99279</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -895,7 +895,7 @@
         <v>136957208</v>
       </c>
       <c r="B4" t="n">
-        <v>99363</v>
+        <v>99364</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1001,7 +1001,7 @@
         <v>136957209</v>
       </c>
       <c r="B5" t="n">
-        <v>99385</v>
+        <v>99386</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1107,7 +1107,7 @@
         <v>136957211</v>
       </c>
       <c r="B6" t="n">
-        <v>110078</v>
+        <v>110079</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1213,7 +1213,7 @@
         <v>136957212</v>
       </c>
       <c r="B7" t="n">
-        <v>110078</v>
+        <v>110079</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>

--- a/artfynd/A 3248-2025 artfynd.xlsx
+++ b/artfynd/A 3248-2025 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136951559</v>
       </c>
       <c r="B2" t="n">
-        <v>99279</v>
+        <v>99285</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -789,7 +789,7 @@
         <v>136957210</v>
       </c>
       <c r="B3" t="n">
-        <v>99279</v>
+        <v>99285</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -895,7 +895,7 @@
         <v>136957208</v>
       </c>
       <c r="B4" t="n">
-        <v>99364</v>
+        <v>99370</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1001,7 +1001,7 @@
         <v>136957209</v>
       </c>
       <c r="B5" t="n">
-        <v>99386</v>
+        <v>99392</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1107,7 +1107,7 @@
         <v>136957211</v>
       </c>
       <c r="B6" t="n">
-        <v>110079</v>
+        <v>110085</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1213,7 +1213,7 @@
         <v>136957212</v>
       </c>
       <c r="B7" t="n">
-        <v>110079</v>
+        <v>110085</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>

--- a/artfynd/A 3248-2025 artfynd.xlsx
+++ b/artfynd/A 3248-2025 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136951559</v>
       </c>
       <c r="B2" t="n">
-        <v>99285</v>
+        <v>99289</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -789,7 +789,7 @@
         <v>136957210</v>
       </c>
       <c r="B3" t="n">
-        <v>99285</v>
+        <v>99289</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -895,7 +895,7 @@
         <v>136957208</v>
       </c>
       <c r="B4" t="n">
-        <v>99370</v>
+        <v>99374</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1001,7 +1001,7 @@
         <v>136957209</v>
       </c>
       <c r="B5" t="n">
-        <v>99392</v>
+        <v>99396</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1107,7 +1107,7 @@
         <v>136957211</v>
       </c>
       <c r="B6" t="n">
-        <v>110085</v>
+        <v>110089</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1213,7 +1213,7 @@
         <v>136957212</v>
       </c>
       <c r="B7" t="n">
-        <v>110085</v>
+        <v>110089</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>

--- a/artfynd/A 3248-2025 artfynd.xlsx
+++ b/artfynd/A 3248-2025 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136951559</v>
       </c>
       <c r="B2" t="n">
-        <v>99289</v>
+        <v>99291</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -789,7 +789,7 @@
         <v>136957210</v>
       </c>
       <c r="B3" t="n">
-        <v>99289</v>
+        <v>99291</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -895,7 +895,7 @@
         <v>136957208</v>
       </c>
       <c r="B4" t="n">
-        <v>99374</v>
+        <v>99376</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1001,7 +1001,7 @@
         <v>136957209</v>
       </c>
       <c r="B5" t="n">
-        <v>99396</v>
+        <v>99398</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1107,7 +1107,7 @@
         <v>136957211</v>
       </c>
       <c r="B6" t="n">
-        <v>110089</v>
+        <v>110091</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1213,7 +1213,7 @@
         <v>136957212</v>
       </c>
       <c r="B7" t="n">
-        <v>110089</v>
+        <v>110091</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>

--- a/artfynd/A 3248-2025 artfynd.xlsx
+++ b/artfynd/A 3248-2025 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136951559</v>
       </c>
       <c r="B2" t="n">
-        <v>99291</v>
+        <v>99293</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -789,7 +789,7 @@
         <v>136957210</v>
       </c>
       <c r="B3" t="n">
-        <v>99291</v>
+        <v>99293</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -895,7 +895,7 @@
         <v>136957208</v>
       </c>
       <c r="B4" t="n">
-        <v>99376</v>
+        <v>99378</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1001,7 +1001,7 @@
         <v>136957209</v>
       </c>
       <c r="B5" t="n">
-        <v>99398</v>
+        <v>99400</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1107,7 +1107,7 @@
         <v>136957211</v>
       </c>
       <c r="B6" t="n">
-        <v>110091</v>
+        <v>110093</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1213,7 +1213,7 @@
         <v>136957212</v>
       </c>
       <c r="B7" t="n">
-        <v>110091</v>
+        <v>110093</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>

--- a/artfynd/A 3248-2025 artfynd.xlsx
+++ b/artfynd/A 3248-2025 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136951559</v>
       </c>
       <c r="B2" t="n">
-        <v>99293</v>
+        <v>99306</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -789,7 +789,7 @@
         <v>136957210</v>
       </c>
       <c r="B3" t="n">
-        <v>99293</v>
+        <v>99306</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -895,7 +895,7 @@
         <v>136957208</v>
       </c>
       <c r="B4" t="n">
-        <v>99378</v>
+        <v>99391</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1001,7 +1001,7 @@
         <v>136957209</v>
       </c>
       <c r="B5" t="n">
-        <v>99400</v>
+        <v>99413</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1107,7 +1107,7 @@
         <v>136957211</v>
       </c>
       <c r="B6" t="n">
-        <v>110093</v>
+        <v>110106</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1213,7 +1213,7 @@
         <v>136957212</v>
       </c>
       <c r="B7" t="n">
-        <v>110093</v>
+        <v>110106</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>

--- a/artfynd/A 3248-2025 artfynd.xlsx
+++ b/artfynd/A 3248-2025 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136951559</v>
       </c>
       <c r="B2" t="n">
-        <v>99306</v>
+        <v>99308</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -789,7 +789,7 @@
         <v>136957210</v>
       </c>
       <c r="B3" t="n">
-        <v>99306</v>
+        <v>99308</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -895,7 +895,7 @@
         <v>136957208</v>
       </c>
       <c r="B4" t="n">
-        <v>99391</v>
+        <v>99393</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1001,7 +1001,7 @@
         <v>136957209</v>
       </c>
       <c r="B5" t="n">
-        <v>99413</v>
+        <v>99415</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1107,7 +1107,7 @@
         <v>136957211</v>
       </c>
       <c r="B6" t="n">
-        <v>110106</v>
+        <v>110108</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1213,7 +1213,7 @@
         <v>136957212</v>
       </c>
       <c r="B7" t="n">
-        <v>110106</v>
+        <v>110108</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>

--- a/artfynd/A 3248-2025 artfynd.xlsx
+++ b/artfynd/A 3248-2025 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136951559</v>
       </c>
       <c r="B2" t="n">
-        <v>99308</v>
+        <v>99311</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -789,7 +789,7 @@
         <v>136957210</v>
       </c>
       <c r="B3" t="n">
-        <v>99308</v>
+        <v>99311</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -895,7 +895,7 @@
         <v>136957208</v>
       </c>
       <c r="B4" t="n">
-        <v>99393</v>
+        <v>99396</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1001,7 +1001,7 @@
         <v>136957209</v>
       </c>
       <c r="B5" t="n">
-        <v>99415</v>
+        <v>99418</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1107,7 +1107,7 @@
         <v>136957211</v>
       </c>
       <c r="B6" t="n">
-        <v>110108</v>
+        <v>110113</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1213,7 +1213,7 @@
         <v>136957212</v>
       </c>
       <c r="B7" t="n">
-        <v>110108</v>
+        <v>110113</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>

--- a/artfynd/A 3248-2025 artfynd.xlsx
+++ b/artfynd/A 3248-2025 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136951559</v>
       </c>
       <c r="B2" t="n">
-        <v>99311</v>
+        <v>99321</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -789,7 +789,7 @@
         <v>136957210</v>
       </c>
       <c r="B3" t="n">
-        <v>99311</v>
+        <v>99321</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -895,7 +895,7 @@
         <v>136957208</v>
       </c>
       <c r="B4" t="n">
-        <v>99396</v>
+        <v>99406</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1001,7 +1001,7 @@
         <v>136957209</v>
       </c>
       <c r="B5" t="n">
-        <v>99418</v>
+        <v>99428</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1107,7 +1107,7 @@
         <v>136957211</v>
       </c>
       <c r="B6" t="n">
-        <v>110113</v>
+        <v>110134</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1213,7 +1213,7 @@
         <v>136957212</v>
       </c>
       <c r="B7" t="n">
-        <v>110113</v>
+        <v>110134</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>

--- a/artfynd/A 3248-2025 artfynd.xlsx
+++ b/artfynd/A 3248-2025 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136951559</v>
       </c>
       <c r="B2" t="n">
-        <v>99321</v>
+        <v>99322</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -789,7 +789,7 @@
         <v>136957210</v>
       </c>
       <c r="B3" t="n">
-        <v>99321</v>
+        <v>99322</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -895,7 +895,7 @@
         <v>136957208</v>
       </c>
       <c r="B4" t="n">
-        <v>99406</v>
+        <v>99407</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1001,7 +1001,7 @@
         <v>136957209</v>
       </c>
       <c r="B5" t="n">
-        <v>99428</v>
+        <v>99429</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1107,7 +1107,7 @@
         <v>136957211</v>
       </c>
       <c r="B6" t="n">
-        <v>110134</v>
+        <v>110135</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1213,7 +1213,7 @@
         <v>136957212</v>
       </c>
       <c r="B7" t="n">
-        <v>110134</v>
+        <v>110135</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>

--- a/artfynd/A 3248-2025 artfynd.xlsx
+++ b/artfynd/A 3248-2025 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136951559</v>
       </c>
       <c r="B2" t="n">
-        <v>99322</v>
+        <v>99327</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -789,7 +789,7 @@
         <v>136957210</v>
       </c>
       <c r="B3" t="n">
-        <v>99322</v>
+        <v>99327</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -895,7 +895,7 @@
         <v>136957208</v>
       </c>
       <c r="B4" t="n">
-        <v>99407</v>
+        <v>99412</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1001,7 +1001,7 @@
         <v>136957209</v>
       </c>
       <c r="B5" t="n">
-        <v>99429</v>
+        <v>99434</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1107,7 +1107,7 @@
         <v>136957211</v>
       </c>
       <c r="B6" t="n">
-        <v>110135</v>
+        <v>110140</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1213,7 +1213,7 @@
         <v>136957212</v>
       </c>
       <c r="B7" t="n">
-        <v>110135</v>
+        <v>110140</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>

--- a/artfynd/A 3248-2025 artfynd.xlsx
+++ b/artfynd/A 3248-2025 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136951559</v>
       </c>
       <c r="B2" t="n">
-        <v>99327</v>
+        <v>99329</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -789,7 +789,7 @@
         <v>136957210</v>
       </c>
       <c r="B3" t="n">
-        <v>99327</v>
+        <v>99329</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -895,7 +895,7 @@
         <v>136957208</v>
       </c>
       <c r="B4" t="n">
-        <v>99412</v>
+        <v>99414</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1001,7 +1001,7 @@
         <v>136957209</v>
       </c>
       <c r="B5" t="n">
-        <v>99434</v>
+        <v>99436</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1107,7 +1107,7 @@
         <v>136957211</v>
       </c>
       <c r="B6" t="n">
-        <v>110140</v>
+        <v>110143</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1213,7 +1213,7 @@
         <v>136957212</v>
       </c>
       <c r="B7" t="n">
-        <v>110140</v>
+        <v>110143</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>

--- a/artfynd/A 3248-2025 artfynd.xlsx
+++ b/artfynd/A 3248-2025 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136951559</v>
       </c>
       <c r="B2" t="n">
-        <v>99329</v>
+        <v>99335</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -789,7 +789,7 @@
         <v>136957210</v>
       </c>
       <c r="B3" t="n">
-        <v>99329</v>
+        <v>99335</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -895,7 +895,7 @@
         <v>136957208</v>
       </c>
       <c r="B4" t="n">
-        <v>99414</v>
+        <v>99420</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1001,7 +1001,7 @@
         <v>136957209</v>
       </c>
       <c r="B5" t="n">
-        <v>99436</v>
+        <v>99442</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1107,7 +1107,7 @@
         <v>136957211</v>
       </c>
       <c r="B6" t="n">
-        <v>110143</v>
+        <v>110149</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1213,7 +1213,7 @@
         <v>136957212</v>
       </c>
       <c r="B7" t="n">
-        <v>110143</v>
+        <v>110149</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>

--- a/artfynd/A 3248-2025 artfynd.xlsx
+++ b/artfynd/A 3248-2025 artfynd.xlsx
@@ -1107,7 +1107,7 @@
         <v>136957211</v>
       </c>
       <c r="B6" t="n">
-        <v>110149</v>
+        <v>110150</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1213,7 +1213,7 @@
         <v>136957212</v>
       </c>
       <c r="B7" t="n">
-        <v>110149</v>
+        <v>110150</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>

--- a/artfynd/A 3248-2025 artfynd.xlsx
+++ b/artfynd/A 3248-2025 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136951559</v>
       </c>
       <c r="B2" t="n">
-        <v>99335</v>
+        <v>99347</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -789,7 +789,7 @@
         <v>136957210</v>
       </c>
       <c r="B3" t="n">
-        <v>99335</v>
+        <v>99347</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -895,7 +895,7 @@
         <v>136957208</v>
       </c>
       <c r="B4" t="n">
-        <v>99420</v>
+        <v>99432</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1001,7 +1001,7 @@
         <v>136957209</v>
       </c>
       <c r="B5" t="n">
-        <v>99442</v>
+        <v>99454</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1107,7 +1107,7 @@
         <v>136957211</v>
       </c>
       <c r="B6" t="n">
-        <v>110150</v>
+        <v>110162</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1213,7 +1213,7 @@
         <v>136957212</v>
       </c>
       <c r="B7" t="n">
-        <v>110150</v>
+        <v>110162</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>

--- a/artfynd/A 3248-2025 artfynd.xlsx
+++ b/artfynd/A 3248-2025 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136951559</v>
       </c>
       <c r="B2" t="n">
-        <v>99347</v>
+        <v>99348</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -789,7 +789,7 @@
         <v>136957210</v>
       </c>
       <c r="B3" t="n">
-        <v>99347</v>
+        <v>99348</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -895,7 +895,7 @@
         <v>136957208</v>
       </c>
       <c r="B4" t="n">
-        <v>99432</v>
+        <v>99433</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1001,7 +1001,7 @@
         <v>136957209</v>
       </c>
       <c r="B5" t="n">
-        <v>99454</v>
+        <v>99455</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1107,7 +1107,7 @@
         <v>136957211</v>
       </c>
       <c r="B6" t="n">
-        <v>110162</v>
+        <v>110163</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1213,7 +1213,7 @@
         <v>136957212</v>
       </c>
       <c r="B7" t="n">
-        <v>110162</v>
+        <v>110163</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>

--- a/artfynd/A 3248-2025 artfynd.xlsx
+++ b/artfynd/A 3248-2025 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136951559</v>
       </c>
       <c r="B2" t="n">
-        <v>99348</v>
+        <v>99351</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -789,7 +789,7 @@
         <v>136957210</v>
       </c>
       <c r="B3" t="n">
-        <v>99348</v>
+        <v>99351</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -895,7 +895,7 @@
         <v>136957208</v>
       </c>
       <c r="B4" t="n">
-        <v>99433</v>
+        <v>99436</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1001,7 +1001,7 @@
         <v>136957209</v>
       </c>
       <c r="B5" t="n">
-        <v>99455</v>
+        <v>99458</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1107,7 +1107,7 @@
         <v>136957211</v>
       </c>
       <c r="B6" t="n">
-        <v>110163</v>
+        <v>110166</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1213,7 +1213,7 @@
         <v>136957212</v>
       </c>
       <c r="B7" t="n">
-        <v>110163</v>
+        <v>110166</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>

--- a/artfynd/A 3248-2025 artfynd.xlsx
+++ b/artfynd/A 3248-2025 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136951559</v>
       </c>
       <c r="B2" t="n">
-        <v>99351</v>
+        <v>99352</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -789,7 +789,7 @@
         <v>136957210</v>
       </c>
       <c r="B3" t="n">
-        <v>99351</v>
+        <v>99352</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -895,7 +895,7 @@
         <v>136957208</v>
       </c>
       <c r="B4" t="n">
-        <v>99436</v>
+        <v>99437</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1001,7 +1001,7 @@
         <v>136957209</v>
       </c>
       <c r="B5" t="n">
-        <v>99458</v>
+        <v>99459</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1107,7 +1107,7 @@
         <v>136957211</v>
       </c>
       <c r="B6" t="n">
-        <v>110166</v>
+        <v>110168</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1213,7 +1213,7 @@
         <v>136957212</v>
       </c>
       <c r="B7" t="n">
-        <v>110166</v>
+        <v>110168</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>

--- a/artfynd/A 3248-2025 artfynd.xlsx
+++ b/artfynd/A 3248-2025 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136951559</v>
       </c>
       <c r="B2" t="n">
-        <v>99352</v>
+        <v>99355</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -789,7 +789,7 @@
         <v>136957210</v>
       </c>
       <c r="B3" t="n">
-        <v>99352</v>
+        <v>99355</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -895,7 +895,7 @@
         <v>136957208</v>
       </c>
       <c r="B4" t="n">
-        <v>99437</v>
+        <v>99440</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1001,7 +1001,7 @@
         <v>136957209</v>
       </c>
       <c r="B5" t="n">
-        <v>99459</v>
+        <v>99462</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1107,7 +1107,7 @@
         <v>136957211</v>
       </c>
       <c r="B6" t="n">
-        <v>110168</v>
+        <v>110172</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1213,7 +1213,7 @@
         <v>136957212</v>
       </c>
       <c r="B7" t="n">
-        <v>110168</v>
+        <v>110172</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
